--- a/outputs/290-27.xlsx
+++ b/outputs/290-27.xlsx
@@ -437,32 +437,36 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -658,2296 +662,2296 @@
   <dimension ref="A14:I139"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="2.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="9.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="4.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="9.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="2.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="9.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="4.22"/>
   </cols>
   <sheetData>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E14" s="2" t="n">
+      <c r="E14" s="3" t="n">
         <v>44082</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="2" t="n">
+      <c r="B16" s="3" t="n">
         <v>44082</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="1"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="4" t="n">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I18" s="1" t="s">
+      <c r="H18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="3" t="n">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I19" s="1" t="s">
+      <c r="H19" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="5" t="n">
+      <c r="B20" s="6" t="n">
         <v>4.2</v>
       </c>
-      <c r="C20" s="5" t="n">
+      <c r="C20" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D20" s="6" t="n">
         <v>2.4</v>
       </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="3" t="n">
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I20" s="1" t="s">
+      <c r="H20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I21" s="1" t="s">
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5" t="n">
+      <c r="B22" s="6"/>
+      <c r="C22" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D22" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="3" t="n">
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I22" s="1" t="s">
+      <c r="H22" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="3" t="n">
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
+      <c r="D23" s="6"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I23" s="1" t="s">
+      <c r="H23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5" t="n">
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="3" t="n">
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I24" s="1" t="s">
+      <c r="H24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E26" s="2" t="n">
+      <c r="E26" s="3" t="n">
         <v>44082</v>
       </c>
-      <c r="F26" s="1"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B28" s="2" t="n">
+      <c r="B28" s="3" t="n">
         <v>44082</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F28" s="1"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="1"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5" t="n">
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="6" t="n">
         <v>2.6</v>
       </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="3" t="n">
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H30" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I30" s="1" t="s">
+      <c r="H30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="3" t="n">
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I31" s="1" t="s">
+      <c r="H31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="4" t="n">
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H32" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I32" s="1" t="s">
+      <c r="H32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I32" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B33" s="5" t="n">
+      <c r="B33" s="6" t="n">
         <v>5.4</v>
       </c>
-      <c r="C33" s="5" t="n">
+      <c r="C33" s="6" t="n">
         <v>3.6</v>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="D33" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="3" t="n">
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H33" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I33" s="1" t="s">
+      <c r="H33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I33" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="4" t="n">
+      <c r="B34" s="6"/>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I34" s="1" t="s">
+      <c r="H34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I34" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="5"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="3" t="n">
+      <c r="B35" s="6"/>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H35" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I35" s="1" t="s">
+      <c r="H35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I35" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="3" t="n">
+      <c r="B36" s="6"/>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I36" s="1" t="s">
+      <c r="H36" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5" t="n">
+      <c r="B37" s="6"/>
+      <c r="C37" s="6" t="n">
         <v>12.8</v>
       </c>
-      <c r="D37" s="5" t="n">
+      <c r="D37" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="3" t="n">
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H37" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I37" s="1" t="s">
+      <c r="H37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I37" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E39" s="2" t="n">
+      <c r="E39" s="3" t="n">
         <v>44082</v>
       </c>
-      <c r="F39" s="1"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B41" s="2" t="n">
+      <c r="B41" s="3" t="n">
         <v>44082</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="F41" s="1"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="3"/>
-      <c r="I41" s="1"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
+      <c r="I41" s="2"/>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="3"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="4"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="4" t="n">
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H43" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I43" s="1" t="s">
+      <c r="H43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I43" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5" t="n">
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I44" s="1" t="s">
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I44" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B45" s="5" t="n">
+      <c r="B45" s="6" t="n">
         <v>11.8</v>
       </c>
-      <c r="C45" s="5" t="n">
+      <c r="C45" s="6" t="n">
         <v>5.6</v>
       </c>
-      <c r="D45" s="5" t="n">
+      <c r="D45" s="6" t="n">
         <v>5.6</v>
       </c>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="4" t="n">
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H45" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I45" s="1" t="s">
+      <c r="H45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I45" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="3" t="n">
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="6"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H46" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I46" s="1" t="s">
+      <c r="H46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I46" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B47" s="5"/>
-      <c r="C47" s="5"/>
-      <c r="D47" s="5"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="4" t="n">
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="H47" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I47" s="1" t="s">
+      <c r="H47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I47" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="4" t="n">
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H48" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I48" s="1" t="s">
+      <c r="H48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I48" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B49" s="5"/>
-      <c r="C49" s="5"/>
-      <c r="D49" s="5"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="3" t="n">
+      <c r="B49" s="6"/>
+      <c r="C49" s="6"/>
+      <c r="D49" s="6"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H49" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I49" s="1" t="s">
+      <c r="H49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I49" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5" t="n">
+      <c r="B50" s="6"/>
+      <c r="C50" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="D50" s="5" t="n">
+      <c r="D50" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="3" t="n">
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H50" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I50" s="1" t="s">
+      <c r="H50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I50" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="3" t="n">
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H51" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I51" s="1" t="s">
+      <c r="H51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I51" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="3" t="n">
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+      <c r="D52" s="2"/>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H52" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I52" s="1" t="s">
+      <c r="H52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I52" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="3"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
+      <c r="A53" s="2"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+      <c r="D53" s="2"/>
+      <c r="E53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="4"/>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
     </row>
     <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E54" s="2" t="n">
+      <c r="E54" s="3" t="n">
         <v>44082</v>
       </c>
-      <c r="F54" s="1"/>
-      <c r="G54" s="3"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="4"/>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
     </row>
     <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="3"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="4"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B56" s="2" t="n">
+      <c r="B56" s="3" t="n">
         <v>44082</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F56" s="1"/>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="1"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="4"/>
+      <c r="H56" s="4"/>
+      <c r="I56" s="2"/>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="3"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="4"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="3" t="n">
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H58" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I58" s="1" t="s">
+      <c r="H58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I58" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B59" s="5"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="5" t="n">
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="3" t="n">
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H59" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I59" s="1" t="s">
+      <c r="H59" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I59" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5" t="n">
+      <c r="B60" s="6"/>
+      <c r="C60" s="6" t="n">
         <v>8.8</v>
       </c>
-      <c r="D60" s="5" t="n">
+      <c r="D60" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="3" t="n">
+      <c r="E60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H60" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I60" s="1" t="s">
+      <c r="H60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I60" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B61" s="5"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="3" t="n">
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+      <c r="E61" s="2"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H61" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I61" s="1" t="s">
+      <c r="H61" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I61" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="3" t="n">
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="2"/>
+      <c r="F62" s="2"/>
+      <c r="G62" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H62" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I62" s="1" t="s">
+      <c r="H62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I62" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B63" s="5" t="n">
+      <c r="B63" s="6" t="n">
         <v>37.2</v>
       </c>
-      <c r="C63" s="5" t="n">
+      <c r="C63" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="D63" s="5" t="n">
+      <c r="D63" s="6" t="n">
         <v>10.8</v>
       </c>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="4" t="n">
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H63" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I63" s="1" t="s">
+      <c r="H63" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I63" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="4" t="n">
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+      <c r="D64" s="2"/>
+      <c r="E64" s="2"/>
+      <c r="F64" s="2"/>
+      <c r="G64" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H64" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I64" s="1" t="s">
+      <c r="H64" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I64" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I65" s="1" t="s">
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+      <c r="D65" s="2"/>
+      <c r="E65" s="2"/>
+      <c r="F65" s="2"/>
+      <c r="G65" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I65" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="3"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
+      <c r="A66" s="2"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+      <c r="D66" s="2"/>
+      <c r="E66" s="2"/>
+      <c r="F66" s="2"/>
+      <c r="G66" s="4"/>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
     </row>
     <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E67" s="2" t="n">
+      <c r="E67" s="3" t="n">
         <v>44082</v>
       </c>
-      <c r="F67" s="1"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
     </row>
     <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
+      <c r="A68" s="2"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="2"/>
+      <c r="F68" s="2"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
     </row>
     <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B69" s="2" t="n">
+      <c r="B69" s="3" t="n">
         <v>44082</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E69" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F69" s="1"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-      <c r="I69" s="1"/>
+      <c r="F69" s="2"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="2"/>
     </row>
     <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="3"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
+      <c r="A70" s="2"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+      <c r="D70" s="2"/>
+      <c r="E70" s="2"/>
+      <c r="F70" s="2"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
     </row>
     <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="3" t="n">
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H71" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I71" s="1" t="s">
+      <c r="H71" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I71" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5" t="n">
+      <c r="B72" s="6"/>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="3" t="n">
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H72" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I72" s="1" t="s">
+      <c r="H72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I72" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B73" s="5"/>
-      <c r="C73" s="5" t="n">
+      <c r="B73" s="6"/>
+      <c r="C73" s="6" t="n">
         <v>6.2</v>
       </c>
-      <c r="D73" s="5" t="n">
+      <c r="D73" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="3" t="n">
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H73" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I73" s="1" t="s">
+      <c r="H73" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I73" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B74" s="5" t="n">
+      <c r="B74" s="6" t="n">
         <v>14.4</v>
       </c>
-      <c r="C74" s="5" t="n">
+      <c r="C74" s="6" t="n">
         <v>8.2</v>
       </c>
-      <c r="D74" s="5" t="n">
+      <c r="D74" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
-      <c r="G74" s="3" t="n">
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I74" s="1" t="s">
+      <c r="H74" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I74" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
+      <c r="A75" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B75" s="1"/>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1"/>
-      <c r="G75" s="3" t="n">
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H75" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I75" s="1" t="s">
+      <c r="H75" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I75" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B76" s="1"/>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="4" t="n">
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H76" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I76" s="1" t="s">
+      <c r="H76" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I76" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B77" s="1"/>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1"/>
-      <c r="G77" s="4" t="n">
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H77" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I77" s="1" t="s">
+      <c r="H77" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I77" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B78" s="1"/>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1"/>
-      <c r="G78" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H78" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I78" s="1" t="s">
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+      <c r="D78" s="2"/>
+      <c r="E78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I78" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B80" s="1" t="n">
+      <c r="B80" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D80" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E80" s="2" t="n">
+      <c r="E80" s="3" t="n">
         <v>44072</v>
       </c>
-      <c r="F80" s="1"/>
-      <c r="G80" s="1"/>
-      <c r="H80" s="1"/>
-      <c r="I80" s="1"/>
+      <c r="F80" s="2"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
     </row>
     <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
+      <c r="A81" s="2"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
+      <c r="D81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
     </row>
     <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B82" s="2" t="n">
+      <c r="B82" s="3" t="n">
         <v>44072</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D82" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E82" s="1" t="s">
+      <c r="E82" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="3"/>
-      <c r="I82" s="1"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="4"/>
+      <c r="I82" s="2"/>
     </row>
     <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
+      <c r="A83" s="2"/>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
     </row>
     <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
+      <c r="A84" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B84" s="1"/>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1"/>
-      <c r="G84" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I84" s="1" t="s">
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
+      <c r="D84" s="2"/>
+      <c r="E84" s="2"/>
+      <c r="F84" s="2"/>
+      <c r="G84" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I84" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B85" s="5"/>
-      <c r="C85" s="5"/>
-      <c r="D85" s="5" t="n">
+      <c r="B85" s="6"/>
+      <c r="C85" s="6"/>
+      <c r="D85" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1"/>
-      <c r="G85" s="3" t="n">
+      <c r="E85" s="2"/>
+      <c r="F85" s="2"/>
+      <c r="G85" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H85" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I85" s="1" t="s">
+      <c r="H85" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I85" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B86" s="5" t="n">
+      <c r="B86" s="6" t="n">
         <v>6.2</v>
       </c>
-      <c r="C86" s="5" t="n">
+      <c r="C86" s="6" t="n">
         <v>4.2</v>
       </c>
-      <c r="D86" s="5" t="n">
+      <c r="D86" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1"/>
-      <c r="G86" s="3" t="n">
+      <c r="E86" s="2"/>
+      <c r="F86" s="2"/>
+      <c r="G86" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H86" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I86" s="1" t="s">
+      <c r="H86" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I86" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B87" s="5"/>
-      <c r="C87" s="5"/>
-      <c r="D87" s="5"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="3" t="n">
+      <c r="B87" s="6"/>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="E87" s="2"/>
+      <c r="F87" s="2"/>
+      <c r="G87" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H87" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I87" s="1" t="s">
+      <c r="H87" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I87" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="s">
+      <c r="A88" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="B88" s="5"/>
-      <c r="C88" s="5"/>
-      <c r="D88" s="5"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1"/>
-      <c r="G88" s="3" t="n">
+      <c r="B88" s="6"/>
+      <c r="C88" s="6"/>
+      <c r="D88" s="6"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H88" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I88" s="1" t="s">
+      <c r="H88" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I88" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B89" s="5"/>
-      <c r="C89" s="5" t="n">
+      <c r="B89" s="6"/>
+      <c r="C89" s="6" t="n">
         <v>11.2</v>
       </c>
-      <c r="D89" s="5" t="n">
+      <c r="D89" s="6" t="n">
         <v>4.8</v>
       </c>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1"/>
-      <c r="G89" s="3" t="n">
+      <c r="E89" s="2"/>
+      <c r="F89" s="2"/>
+      <c r="G89" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H89" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I89" s="1" t="s">
+      <c r="H89" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I89" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="3"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
+      <c r="A90" s="2"/>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
+      <c r="D90" s="2"/>
+      <c r="E90" s="2"/>
+      <c r="F90" s="2"/>
+      <c r="G90" s="4"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
     </row>
     <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B91" s="1" t="n">
+      <c r="B91" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D91" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E91" s="2" t="n">
+      <c r="E91" s="3" t="n">
         <v>44072</v>
       </c>
-      <c r="F91" s="1"/>
-      <c r="G91" s="3"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="4"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
     </row>
     <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
+      <c r="A92" s="2"/>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
+      <c r="D92" s="2"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="4"/>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
     </row>
     <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
+      <c r="A93" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B93" s="2" t="n">
+      <c r="B93" s="3" t="n">
         <v>44072</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="D93" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E93" s="1" t="s">
+      <c r="E93" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F93" s="1"/>
-      <c r="G93" s="3"/>
-      <c r="H93" s="3"/>
-      <c r="I93" s="1"/>
+      <c r="F93" s="2"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="4"/>
+      <c r="I93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="3"/>
-      <c r="H94" s="1"/>
-      <c r="I94" s="1"/>
+      <c r="A94" s="2"/>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
+      <c r="D94" s="2"/>
+      <c r="E94" s="2"/>
+      <c r="F94" s="2"/>
+      <c r="G94" s="4"/>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
     </row>
     <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
+      <c r="A95" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B95" s="5"/>
-      <c r="C95" s="5"/>
-      <c r="D95" s="5" t="n">
+      <c r="B95" s="6"/>
+      <c r="C95" s="6"/>
+      <c r="D95" s="6" t="n">
         <v>3.6</v>
       </c>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H95" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I95" s="1" t="s">
+      <c r="E95" s="2"/>
+      <c r="F95" s="2"/>
+      <c r="G95" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I95" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
+      <c r="A96" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B96" s="5"/>
-      <c r="C96" s="5" t="n">
+      <c r="B96" s="6"/>
+      <c r="C96" s="6" t="n">
         <v>4.4</v>
       </c>
-      <c r="D96" s="5" t="n">
+      <c r="D96" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1"/>
-      <c r="G96" s="3" t="n">
+      <c r="E96" s="2"/>
+      <c r="F96" s="2"/>
+      <c r="G96" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H96" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I96" s="1" t="s">
+      <c r="H96" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I96" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
+      <c r="A97" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B97" s="5"/>
-      <c r="C97" s="5"/>
-      <c r="D97" s="5"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
-      <c r="G97" s="3" t="n">
+      <c r="B97" s="6"/>
+      <c r="C97" s="6"/>
+      <c r="D97" s="6"/>
+      <c r="E97" s="2"/>
+      <c r="F97" s="2"/>
+      <c r="G97" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H97" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I97" s="1" t="s">
+      <c r="H97" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I97" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="6" t="s">
+      <c r="A98" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B98" s="5" t="n">
+      <c r="B98" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="C98" s="5" t="n">
+      <c r="C98" s="6" t="n">
         <v>4.2</v>
       </c>
-      <c r="D98" s="5" t="n">
+      <c r="D98" s="6" t="n">
         <v>3.2</v>
       </c>
-      <c r="E98" s="1"/>
-      <c r="F98" s="1"/>
-      <c r="G98" s="3" t="n">
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H98" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I98" s="1" t="s">
+      <c r="H98" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I98" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
+      <c r="A99" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B99" s="1"/>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1"/>
-      <c r="G99" s="3" t="n">
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
+      <c r="D99" s="2"/>
+      <c r="E99" s="2"/>
+      <c r="F99" s="2"/>
+      <c r="G99" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H99" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I99" s="1" t="s">
+      <c r="H99" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I99" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
+      <c r="A100" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B100" s="1"/>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="3" t="n">
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
+      <c r="D100" s="2"/>
+      <c r="E100" s="2"/>
+      <c r="F100" s="2"/>
+      <c r="G100" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H100" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I100" s="1" t="s">
+      <c r="H100" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I100" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
+      <c r="A101" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
-      <c r="F101" s="1"/>
-      <c r="G101" s="4" t="n">
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
+      <c r="D101" s="2"/>
+      <c r="E101" s="2"/>
+      <c r="F101" s="2"/>
+      <c r="G101" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H101" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I101" s="1" t="s">
+      <c r="H101" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I101" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1"/>
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="1"/>
-      <c r="F102" s="1"/>
-      <c r="G102" s="3"/>
-      <c r="H102" s="1"/>
-      <c r="I102" s="1"/>
+      <c r="A102" s="2"/>
+      <c r="B102" s="2"/>
+      <c r="C102" s="2"/>
+      <c r="D102" s="2"/>
+      <c r="E102" s="2"/>
+      <c r="F102" s="2"/>
+      <c r="G102" s="4"/>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
     </row>
     <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="s">
+      <c r="A103" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B103" s="1" t="n">
+      <c r="B103" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C103" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="D103" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E103" s="2" t="n">
+      <c r="E103" s="3" t="n">
         <v>44072</v>
       </c>
-      <c r="F103" s="1"/>
-      <c r="G103" s="3"/>
-      <c r="H103" s="1"/>
-      <c r="I103" s="1"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
     </row>
     <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1"/>
-      <c r="B104" s="1"/>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
-      <c r="F104" s="1"/>
-      <c r="G104" s="3"/>
-      <c r="H104" s="1"/>
-      <c r="I104" s="1"/>
+      <c r="A104" s="2"/>
+      <c r="B104" s="2"/>
+      <c r="C104" s="2"/>
+      <c r="D104" s="2"/>
+      <c r="E104" s="2"/>
+      <c r="F104" s="2"/>
+      <c r="G104" s="4"/>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
     </row>
     <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
+      <c r="A105" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B105" s="2" t="n">
+      <c r="B105" s="3" t="n">
         <v>44072</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C105" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D105" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E105" s="1" t="s">
+      <c r="E105" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F105" s="1"/>
-      <c r="G105" s="3"/>
-      <c r="H105" s="3"/>
-      <c r="I105" s="1"/>
+      <c r="F105" s="2"/>
+      <c r="G105" s="4"/>
+      <c r="H105" s="4"/>
+      <c r="I105" s="2"/>
     </row>
     <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1"/>
-      <c r="B106" s="1"/>
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1"/>
-      <c r="G106" s="3"/>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
+      <c r="A106" s="2"/>
+      <c r="B106" s="2"/>
+      <c r="C106" s="2"/>
+      <c r="D106" s="2"/>
+      <c r="E106" s="2"/>
+      <c r="F106" s="2"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
     </row>
     <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
+      <c r="A107" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B107" s="5" t="n">
+      <c r="B107" s="6" t="n">
         <v>8.6</v>
       </c>
-      <c r="C107" s="5" t="n">
+      <c r="C107" s="6" t="n">
         <v>3.4</v>
       </c>
-      <c r="D107" s="5" t="n">
+      <c r="D107" s="6" t="n">
         <v>2.6</v>
       </c>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1"/>
-      <c r="G107" s="3" t="n">
+      <c r="E107" s="2"/>
+      <c r="F107" s="2"/>
+      <c r="G107" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H107" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I107" s="1" t="s">
+      <c r="H107" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I107" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
+      <c r="A108" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B108" s="5"/>
-      <c r="C108" s="5"/>
-      <c r="D108" s="5"/>
-      <c r="E108" s="1"/>
-      <c r="F108" s="1"/>
-      <c r="G108" s="3" t="n">
+      <c r="B108" s="6"/>
+      <c r="C108" s="6"/>
+      <c r="D108" s="6"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H108" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I108" s="1" t="s">
+      <c r="H108" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I108" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="s">
+      <c r="A109" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="B109" s="5"/>
-      <c r="C109" s="5"/>
-      <c r="D109" s="5" t="n">
+      <c r="B109" s="6"/>
+      <c r="C109" s="6"/>
+      <c r="D109" s="6" t="n">
         <v>2.2</v>
       </c>
-      <c r="E109" s="1"/>
-      <c r="F109" s="1"/>
-      <c r="G109" s="3" t="n">
+      <c r="E109" s="2"/>
+      <c r="F109" s="2"/>
+      <c r="G109" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H109" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I109" s="1" t="s">
+      <c r="H109" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I109" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="s">
+      <c r="A110" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B110" s="5"/>
-      <c r="C110" s="5"/>
-      <c r="D110" s="5"/>
-      <c r="E110" s="1"/>
-      <c r="F110" s="1"/>
-      <c r="G110" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I110" s="1" t="s">
+      <c r="B110" s="6"/>
+      <c r="C110" s="6"/>
+      <c r="D110" s="6"/>
+      <c r="E110" s="2"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I110" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="s">
+      <c r="A111" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B111" s="5"/>
-      <c r="C111" s="5" t="n">
+      <c r="B111" s="6"/>
+      <c r="C111" s="6" t="n">
         <v>2.6</v>
       </c>
-      <c r="D111" s="5" t="n">
+      <c r="D111" s="6" t="n">
         <v>2.1</v>
       </c>
-      <c r="E111" s="1"/>
-      <c r="F111" s="1"/>
-      <c r="G111" s="3" t="n">
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
+      <c r="G111" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H111" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I111" s="1" t="s">
+      <c r="H111" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I111" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="s">
+      <c r="A112" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
-      <c r="E112" s="1"/>
-      <c r="F112" s="1"/>
-      <c r="G112" s="3" t="n">
+      <c r="B112" s="2"/>
+      <c r="C112" s="2"/>
+      <c r="D112" s="2"/>
+      <c r="E112" s="2"/>
+      <c r="F112" s="2"/>
+      <c r="G112" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H112" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I112" s="1" t="s">
+      <c r="H112" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I112" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1"/>
-      <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-      <c r="E113" s="1"/>
-      <c r="F113" s="1"/>
-      <c r="G113" s="3"/>
-      <c r="H113" s="1"/>
-      <c r="I113" s="1"/>
+      <c r="A113" s="2"/>
+      <c r="B113" s="2"/>
+      <c r="C113" s="2"/>
+      <c r="D113" s="2"/>
+      <c r="E113" s="2"/>
+      <c r="F113" s="2"/>
+      <c r="G113" s="4"/>
+      <c r="H113" s="2"/>
+      <c r="I113" s="2"/>
     </row>
     <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="s">
+      <c r="A114" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B114" s="1" t="n">
+      <c r="B114" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C114" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D114" s="1" t="s">
+      <c r="D114" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E114" s="2" t="n">
+      <c r="E114" s="3" t="n">
         <v>44072</v>
       </c>
-      <c r="F114" s="1"/>
-      <c r="G114" s="3"/>
-      <c r="H114" s="1"/>
-      <c r="I114" s="1"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="4"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
     </row>
     <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1"/>
-      <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
-      <c r="E115" s="1"/>
-      <c r="F115" s="1"/>
-      <c r="G115" s="3"/>
-      <c r="H115" s="1"/>
-      <c r="I115" s="1"/>
+      <c r="A115" s="2"/>
+      <c r="B115" s="2"/>
+      <c r="C115" s="2"/>
+      <c r="D115" s="2"/>
+      <c r="E115" s="2"/>
+      <c r="F115" s="2"/>
+      <c r="G115" s="4"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2"/>
     </row>
     <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="s">
+      <c r="A116" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B116" s="2" t="n">
+      <c r="B116" s="3" t="n">
         <v>44072</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C116" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="D116" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E116" s="1" t="s">
+      <c r="E116" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F116" s="1"/>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
-      <c r="I116" s="1"/>
+      <c r="F116" s="2"/>
+      <c r="G116" s="4"/>
+      <c r="H116" s="4"/>
+      <c r="I116" s="2"/>
     </row>
     <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1"/>
-      <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-      <c r="E117" s="1"/>
-      <c r="F117" s="1"/>
-      <c r="G117" s="3"/>
-      <c r="H117" s="1"/>
-      <c r="I117" s="1"/>
+      <c r="A117" s="2"/>
+      <c r="B117" s="2"/>
+      <c r="C117" s="2"/>
+      <c r="D117" s="2"/>
+      <c r="E117" s="2"/>
+      <c r="F117" s="2"/>
+      <c r="G117" s="4"/>
+      <c r="H117" s="2"/>
+      <c r="I117" s="2"/>
     </row>
     <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="1" t="s">
+      <c r="A118" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B118" s="5" t="n">
+      <c r="B118" s="6" t="n">
         <v>7.4</v>
       </c>
-      <c r="C118" s="5" t="n">
+      <c r="C118" s="6" t="n">
         <v>5.2</v>
       </c>
-      <c r="D118" s="5" t="n">
+      <c r="D118" s="6" t="n">
         <v>3.8</v>
       </c>
-      <c r="E118" s="1"/>
-      <c r="F118" s="1"/>
-      <c r="G118" s="3" t="n">
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H118" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I118" s="1" t="s">
+      <c r="H118" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I118" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="s">
+      <c r="A119" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B119" s="5"/>
-      <c r="C119" s="5"/>
-      <c r="D119" s="5"/>
-      <c r="E119" s="1"/>
-      <c r="F119" s="1"/>
-      <c r="G119" s="3" t="n">
+      <c r="B119" s="6"/>
+      <c r="C119" s="6"/>
+      <c r="D119" s="6"/>
+      <c r="E119" s="2"/>
+      <c r="F119" s="2"/>
+      <c r="G119" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H119" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I119" s="1" t="s">
+      <c r="H119" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I119" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="s">
+      <c r="A120" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B120" s="5"/>
-      <c r="C120" s="5" t="n">
+      <c r="B120" s="6"/>
+      <c r="C120" s="6" t="n">
         <v>21.2</v>
       </c>
-      <c r="D120" s="5" t="n">
+      <c r="D120" s="6" t="n">
         <v>12.8</v>
       </c>
-      <c r="E120" s="1"/>
-      <c r="F120" s="1"/>
-      <c r="G120" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H120" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I120" s="1" t="s">
+      <c r="E120" s="2"/>
+      <c r="F120" s="2"/>
+      <c r="G120" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H120" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I120" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1" t="s">
+      <c r="A121" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B121" s="5"/>
-      <c r="C121" s="5"/>
-      <c r="D121" s="5"/>
-      <c r="E121" s="1"/>
-      <c r="F121" s="1"/>
-      <c r="G121" s="3" t="n">
+      <c r="B121" s="6"/>
+      <c r="C121" s="6"/>
+      <c r="D121" s="6"/>
+      <c r="E121" s="2"/>
+      <c r="F121" s="2"/>
+      <c r="G121" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H121" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I121" s="1" t="s">
+      <c r="H121" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I121" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1" t="s">
+      <c r="A122" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B122" s="5"/>
-      <c r="C122" s="5"/>
-      <c r="D122" s="5"/>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1"/>
-      <c r="G122" s="4" t="n">
+      <c r="B122" s="6"/>
+      <c r="C122" s="6"/>
+      <c r="D122" s="6"/>
+      <c r="E122" s="2"/>
+      <c r="F122" s="2"/>
+      <c r="G122" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="H122" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I122" s="1" t="s">
+      <c r="H122" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I122" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="1" t="s">
+      <c r="A123" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B123" s="5"/>
-      <c r="C123" s="5"/>
-      <c r="D123" s="5"/>
-      <c r="E123" s="1"/>
-      <c r="F123" s="1"/>
-      <c r="G123" s="3" t="n">
+      <c r="B123" s="6"/>
+      <c r="C123" s="6"/>
+      <c r="D123" s="6"/>
+      <c r="E123" s="2"/>
+      <c r="F123" s="2"/>
+      <c r="G123" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H123" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I123" s="1" t="s">
+      <c r="H123" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I123" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="1" t="s">
+      <c r="A124" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B124" s="5"/>
-      <c r="C124" s="5"/>
-      <c r="D124" s="5"/>
-      <c r="E124" s="1"/>
-      <c r="F124" s="1"/>
-      <c r="G124" s="4" t="n">
+      <c r="B124" s="6"/>
+      <c r="C124" s="6"/>
+      <c r="D124" s="6"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="H124" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I124" s="1" t="s">
+      <c r="H124" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I124" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="1" t="s">
+      <c r="A125" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B125" s="5"/>
-      <c r="C125" s="5"/>
-      <c r="D125" s="5" t="n">
+      <c r="B125" s="6"/>
+      <c r="C125" s="6"/>
+      <c r="D125" s="6" t="n">
         <v>6.4</v>
       </c>
-      <c r="E125" s="1"/>
-      <c r="F125" s="1"/>
-      <c r="G125" s="4" t="n">
+      <c r="E125" s="2"/>
+      <c r="F125" s="2"/>
+      <c r="G125" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="H125" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I125" s="1" t="s">
+      <c r="H125" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I125" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="1" t="s">
+      <c r="A126" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
-      <c r="F126" s="1"/>
-      <c r="G126" s="3" t="n">
+      <c r="B126" s="2"/>
+      <c r="C126" s="2"/>
+      <c r="D126" s="2"/>
+      <c r="E126" s="2"/>
+      <c r="F126" s="2"/>
+      <c r="G126" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H126" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I126" s="1" t="s">
+      <c r="H126" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I126" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="1"/>
-      <c r="B127" s="1"/>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
-      <c r="E127" s="1"/>
-      <c r="F127" s="1"/>
-      <c r="G127" s="3"/>
-      <c r="H127" s="1"/>
-      <c r="I127" s="1"/>
+      <c r="A127" s="2"/>
+      <c r="B127" s="2"/>
+      <c r="C127" s="2"/>
+      <c r="D127" s="2"/>
+      <c r="E127" s="2"/>
+      <c r="F127" s="2"/>
+      <c r="G127" s="4"/>
+      <c r="H127" s="2"/>
+      <c r="I127" s="2"/>
     </row>
     <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="1" t="s">
+      <c r="A128" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B128" s="1" t="n">
-        <v>6</v>
-      </c>
-      <c r="C128" s="1" t="s">
+      <c r="B128" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="D128" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E128" s="2" t="n">
+      <c r="E128" s="3" t="n">
         <v>44072</v>
       </c>
-      <c r="F128" s="1"/>
-      <c r="G128" s="3"/>
-      <c r="H128" s="1"/>
-      <c r="I128" s="1"/>
+      <c r="F128" s="2"/>
+      <c r="G128" s="4"/>
+      <c r="H128" s="2"/>
+      <c r="I128" s="2"/>
     </row>
     <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="1"/>
-      <c r="B129" s="1"/>
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
-      <c r="E129" s="1"/>
-      <c r="F129" s="1"/>
-      <c r="G129" s="3"/>
-      <c r="H129" s="1"/>
-      <c r="I129" s="1"/>
+      <c r="A129" s="2"/>
+      <c r="B129" s="2"/>
+      <c r="C129" s="2"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="2"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="4"/>
+      <c r="H129" s="2"/>
+      <c r="I129" s="2"/>
     </row>
     <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="1" t="s">
+      <c r="A130" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B130" s="2" t="n">
+      <c r="B130" s="3" t="n">
         <v>44072</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C130" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D130" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E130" s="1" t="s">
+      <c r="E130" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F130" s="1"/>
-      <c r="G130" s="3"/>
-      <c r="H130" s="3"/>
-      <c r="I130" s="1"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="4"/>
+      <c r="H130" s="4"/>
+      <c r="I130" s="2"/>
     </row>
     <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
-      <c r="E131" s="1"/>
-      <c r="F131" s="1"/>
-      <c r="G131" s="3"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
+      <c r="A131" s="2"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
+      <c r="D131" s="2"/>
+      <c r="E131" s="2"/>
+      <c r="F131" s="2"/>
+      <c r="G131" s="4"/>
+      <c r="H131" s="2"/>
+      <c r="I131" s="2"/>
     </row>
     <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="1" t="s">
+      <c r="A132" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B132" s="1"/>
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
-      <c r="E132" s="1"/>
-      <c r="F132" s="1"/>
-      <c r="G132" s="3" t="n">
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2"/>
+      <c r="F132" s="2"/>
+      <c r="G132" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="H132" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I132" s="1" t="s">
+      <c r="H132" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I132" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="1" t="s">
+      <c r="A133" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B133" s="1"/>
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
-      <c r="E133" s="1"/>
-      <c r="F133" s="1"/>
-      <c r="G133" s="3" t="n">
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2"/>
+      <c r="F133" s="2"/>
+      <c r="G133" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="H133" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I133" s="1" t="s">
+      <c r="H133" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I133" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="1" t="s">
+      <c r="A134" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B134" s="5"/>
-      <c r="C134" s="5"/>
-      <c r="D134" s="5" t="n">
+      <c r="B134" s="6"/>
+      <c r="C134" s="6"/>
+      <c r="D134" s="6" t="n">
         <v>4.8</v>
       </c>
-      <c r="E134" s="1"/>
-      <c r="F134" s="1"/>
-      <c r="G134" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="H134" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I134" s="1" t="s">
+      <c r="E134" s="2"/>
+      <c r="F134" s="2"/>
+      <c r="G134" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I134" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="1" t="s">
+      <c r="A135" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B135" s="5" t="n">
+      <c r="B135" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C135" s="5" t="n">
+      <c r="C135" s="6" t="n">
         <v>2.6</v>
       </c>
-      <c r="D135" s="5" t="n">
+      <c r="D135" s="6" t="n">
         <v>2.4</v>
       </c>
-      <c r="E135" s="1"/>
-      <c r="F135" s="1"/>
-      <c r="G135" s="3" t="n">
+      <c r="E135" s="2"/>
+      <c r="F135" s="2"/>
+      <c r="G135" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H135" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I135" s="1" t="s">
+      <c r="H135" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I135" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="1" t="s">
+      <c r="A136" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B136" s="5"/>
-      <c r="C136" s="5" t="n">
+      <c r="B136" s="6"/>
+      <c r="C136" s="6" t="n">
         <v>3.4</v>
       </c>
-      <c r="D136" s="5" t="n">
+      <c r="D136" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E136" s="1"/>
-      <c r="F136" s="1"/>
-      <c r="G136" s="3" t="n">
+      <c r="E136" s="2"/>
+      <c r="F136" s="2"/>
+      <c r="G136" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="H136" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I136" s="1" t="s">
+      <c r="H136" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I136" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="1" t="s">
+      <c r="A137" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B137" s="1"/>
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
-      <c r="E137" s="1"/>
-      <c r="F137" s="1"/>
-      <c r="G137" s="3" t="n">
+      <c r="B137" s="2"/>
+      <c r="C137" s="2"/>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2"/>
+      <c r="F137" s="2"/>
+      <c r="G137" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="H137" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I137" s="1" t="s">
+      <c r="H137" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I137" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H138" s="1"/>
-      <c r="I138" s="1"/>
+      <c r="H138" s="2"/>
+      <c r="I138" s="2"/>
     </row>
     <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H139" s="1"/>
-      <c r="I139" s="1"/>
+      <c r="H139" s="2"/>
+      <c r="I139" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/outputs/290-27.xlsx
+++ b/outputs/290-27.xlsx
@@ -20,11 +20,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="113">
   <si>
     <t xml:space="preserve">NAME</t>
   </si>
   <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Clm 12500n2l</t>
   </si>
   <si>
@@ -61,6 +64,9 @@
     <t xml:space="preserve">TROIS PONTS</t>
   </si>
   <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Clm 5000b</t>
   </si>
   <si>
@@ -94,6 +100,9 @@
     <t xml:space="preserve">BREZNO</t>
   </si>
   <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
     <t xml:space="preserve">OClm 8500</t>
   </si>
   <si>
@@ -133,6 +142,9 @@
     <t xml:space="preserve">OUR CLOSURE</t>
   </si>
   <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Clm 20000b</t>
   </si>
   <si>
@@ -166,6 +178,9 @@
     <t xml:space="preserve">SPETTACOLI</t>
   </si>
   <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alw 32000n1x</t>
   </si>
   <si>
@@ -196,6 +211,9 @@
     <t xml:space="preserve">ROLLING MO</t>
   </si>
   <si>
+    <t xml:space="preserve"> 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Clm 4000b</t>
   </si>
   <si>
@@ -223,6 +241,9 @@
     <t xml:space="preserve">THE PET</t>
   </si>
   <si>
+    <t xml:space="preserve"> 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Clm 4000n2l</t>
   </si>
   <si>
@@ -250,6 +271,9 @@
     <t xml:space="preserve">RUN FOR A MILLION</t>
   </si>
   <si>
+    <t xml:space="preserve"> 4</t>
+  </si>
+  <si>
     <t xml:space="preserve">Clm 20000</t>
   </si>
   <si>
@@ -277,6 +301,9 @@
     <t xml:space="preserve">BORN TO REIGN</t>
   </si>
   <si>
+    <t xml:space="preserve"> 5</t>
+  </si>
+  <si>
     <t xml:space="preserve">GG 5</t>
   </si>
   <si>
@@ -305,6 +332,9 @@
   </si>
   <si>
     <t xml:space="preserve">INVERTIGO</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 6</t>
   </si>
   <si>
     <t xml:space="preserve">Clm 16000</t>
@@ -676,14 +706,14 @@
       <c r="A14" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B14" s="2" t="n">
+      <c r="B14" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="3" t="n">
         <v>44082</v>
@@ -706,19 +736,19 @@
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>44082</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -738,7 +768,7 @@
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
@@ -749,15 +779,15 @@
         <v>7</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -768,15 +798,15 @@
         <v>5</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20" s="6" t="n">
         <v>4.2</v>
@@ -793,15 +823,15 @@
         <v>2</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B21" s="6"/>
       <c r="C21" s="6"/>
@@ -812,15 +842,15 @@
         <v>6</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="n">
@@ -835,15 +865,15 @@
         <v>4</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B23" s="6"/>
       <c r="C23" s="6"/>
@@ -854,15 +884,15 @@
         <v>1</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B24" s="6"/>
       <c r="C24" s="6"/>
@@ -875,10 +905,10 @@
         <v>3</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -896,14 +926,14 @@
       <c r="A26" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B26" s="2" t="n">
-        <v>2</v>
+      <c r="B26" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E26" s="3" t="n">
         <v>44082</v>
@@ -926,19 +956,19 @@
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>44082</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>13</v>
       </c>
       <c r="F28" s="2"/>
       <c r="G28" s="4"/>
@@ -958,7 +988,7 @@
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B30" s="6"/>
       <c r="C30" s="6"/>
@@ -971,15 +1001,15 @@
         <v>3</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B31" s="6"/>
       <c r="C31" s="6"/>
@@ -990,15 +1020,15 @@
         <v>2</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B32" s="6"/>
       <c r="C32" s="6"/>
@@ -1009,15 +1039,15 @@
         <v>7</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B33" s="6" t="n">
         <v>5.4</v>
@@ -1034,15 +1064,15 @@
         <v>1</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B34" s="6"/>
       <c r="C34" s="6"/>
@@ -1053,15 +1083,15 @@
         <v>8</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B35" s="6"/>
       <c r="C35" s="6"/>
@@ -1072,15 +1102,15 @@
         <v>5</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B36" s="6"/>
       <c r="C36" s="6"/>
@@ -1091,15 +1121,15 @@
         <v>4</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="n">
@@ -1114,10 +1144,10 @@
         <v>5</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1135,14 +1165,14 @@
       <c r="A39" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="2" t="n">
-        <v>3</v>
+      <c r="B39" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>44082</v>
@@ -1165,19 +1195,19 @@
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B41" s="3" t="n">
         <v>44082</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F41" s="2"/>
       <c r="G41" s="4"/>
@@ -1197,7 +1227,7 @@
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -1208,15 +1238,15 @@
         <v>7</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B44" s="6"/>
       <c r="C44" s="6"/>
@@ -1229,15 +1259,15 @@
         <v>6</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B45" s="6" t="n">
         <v>11.8</v>
@@ -1254,15 +1284,15 @@
         <v>8</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B46" s="6"/>
       <c r="C46" s="6"/>
@@ -1273,15 +1303,15 @@
         <v>5</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I46" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="6"/>
@@ -1292,15 +1322,15 @@
         <v>10</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B48" s="6"/>
       <c r="C48" s="6"/>
@@ -1311,15 +1341,15 @@
         <v>9</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I48" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B49" s="6"/>
       <c r="C49" s="6"/>
@@ -1330,15 +1360,15 @@
         <v>2</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I49" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="6" t="n">
@@ -1353,15 +1383,15 @@
         <v>1</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I50" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -1372,15 +1402,15 @@
         <v>3</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I51" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -1391,10 +1421,10 @@
         <v>4</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I52" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1412,14 +1442,14 @@
       <c r="A54" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B54" s="2" t="n">
-        <v>4</v>
+      <c r="B54" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>44082</v>
@@ -1442,19 +1472,19 @@
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B56" s="3" t="n">
         <v>44082</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F56" s="2"/>
       <c r="G56" s="4"/>
@@ -1474,7 +1504,7 @@
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -1485,15 +1515,15 @@
         <v>1</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I58" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B59" s="6"/>
       <c r="C59" s="6"/>
@@ -1506,15 +1536,15 @@
         <v>5</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B60" s="6"/>
       <c r="C60" s="6" t="n">
@@ -1529,15 +1559,15 @@
         <v>4</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I60" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B61" s="6"/>
       <c r="C61" s="6"/>
@@ -1548,15 +1578,15 @@
         <v>3</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I61" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B62" s="6"/>
       <c r="C62" s="6"/>
@@ -1567,15 +1597,15 @@
         <v>2</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I62" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B63" s="6" t="n">
         <v>37.2</v>
@@ -1592,15 +1622,15 @@
         <v>8</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
@@ -1611,15 +1641,15 @@
         <v>7</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
@@ -1630,10 +1660,10 @@
         <v>6</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I65" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1651,14 +1681,14 @@
       <c r="A67" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B67" s="2" t="n">
-        <v>5</v>
+      <c r="B67" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E67" s="3" t="n">
         <v>44082</v>
@@ -1681,19 +1711,19 @@
     </row>
     <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B69" s="3" t="n">
         <v>44082</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="4"/>
@@ -1713,7 +1743,7 @@
     </row>
     <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
@@ -1724,15 +1754,15 @@
         <v>2</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B72" s="6"/>
       <c r="C72" s="6"/>
@@ -1745,15 +1775,15 @@
         <v>4</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I72" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B73" s="6"/>
       <c r="C73" s="6" t="n">
@@ -1768,15 +1798,15 @@
         <v>1</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I73" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B74" s="6" t="n">
         <v>14.4</v>
@@ -1793,15 +1823,15 @@
         <v>3</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I74" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
@@ -1812,15 +1842,15 @@
         <v>5</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -1831,15 +1861,15 @@
         <v>7</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I76" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -1850,15 +1880,15 @@
         <v>8</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I77" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -1869,24 +1899,24 @@
         <v>6</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I78" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B80" s="2" t="n">
-        <v>1</v>
+      <c r="B80" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>44072</v>
@@ -1909,19 +1939,19 @@
     </row>
     <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B82" s="3" t="n">
         <v>44072</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -1941,7 +1971,7 @@
     </row>
     <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -1952,15 +1982,15 @@
         <v>6</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I84" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B85" s="6"/>
       <c r="C85" s="6"/>
@@ -1973,15 +2003,15 @@
         <v>4</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I85" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B86" s="6" t="n">
         <v>6.2</v>
@@ -1998,15 +2028,15 @@
         <v>2</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I86" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B87" s="6"/>
       <c r="C87" s="6"/>
@@ -2017,15 +2047,15 @@
         <v>5</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I87" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B88" s="6"/>
       <c r="C88" s="6"/>
@@ -2036,15 +2066,15 @@
         <v>1</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I88" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="B89" s="6"/>
       <c r="C89" s="6" t="n">
@@ -2059,10 +2089,10 @@
         <v>3</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2080,14 +2110,14 @@
       <c r="A91" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B91" s="2" t="n">
-        <v>2</v>
+      <c r="B91" s="2" t="s">
+        <v>73</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E91" s="3" t="n">
         <v>44072</v>
@@ -2110,19 +2140,19 @@
     </row>
     <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B93" s="3" t="n">
         <v>44072</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="4"/>
@@ -2142,7 +2172,7 @@
     </row>
     <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B95" s="6"/>
       <c r="C95" s="6"/>
@@ -2155,15 +2185,15 @@
         <v>6</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I95" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B96" s="6"/>
       <c r="C96" s="6" t="n">
@@ -2178,15 +2208,15 @@
         <v>3</v>
       </c>
       <c r="H96" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I96" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="B97" s="6"/>
       <c r="C97" s="6"/>
@@ -2197,15 +2227,15 @@
         <v>2</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I97" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="7" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B98" s="6" t="n">
         <v>11</v>
@@ -2222,15 +2252,15 @@
         <v>1</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -2241,15 +2271,15 @@
         <v>4</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I99" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -2260,15 +2290,15 @@
         <v>5</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I100" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -2279,10 +2309,10 @@
         <v>7</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I101" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2300,14 +2330,14 @@
       <c r="A103" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B103" s="2" t="n">
-        <v>4</v>
+      <c r="B103" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E103" s="3" t="n">
         <v>44072</v>
@@ -2330,19 +2360,19 @@
     </row>
     <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B105" s="3" t="n">
         <v>44072</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="F105" s="2"/>
       <c r="G105" s="4"/>
@@ -2362,7 +2392,7 @@
     </row>
     <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="B107" s="6" t="n">
         <v>8.6</v>
@@ -2379,15 +2409,15 @@
         <v>5</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="B108" s="6"/>
       <c r="C108" s="6"/>
@@ -2398,15 +2428,15 @@
         <v>4</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B109" s="6"/>
       <c r="C109" s="6"/>
@@ -2419,15 +2449,15 @@
         <v>1</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="B110" s="6"/>
       <c r="C110" s="6"/>
@@ -2438,15 +2468,15 @@
         <v>6</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I110" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B111" s="6"/>
       <c r="C111" s="6" t="n">
@@ -2461,15 +2491,15 @@
         <v>2</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -2480,10 +2510,10 @@
         <v>3</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2501,14 +2531,14 @@
       <c r="A114" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B114" s="2" t="n">
-        <v>5</v>
+      <c r="B114" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E114" s="3" t="n">
         <v>44072</v>
@@ -2531,19 +2561,19 @@
     </row>
     <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B116" s="3" t="n">
         <v>44072</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="4"/>
@@ -2563,7 +2593,7 @@
     </row>
     <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="B118" s="6" t="n">
         <v>7.4</v>
@@ -2580,15 +2610,15 @@
         <v>3</v>
       </c>
       <c r="H118" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I118" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B119" s="6"/>
       <c r="C119" s="6"/>
@@ -2599,15 +2629,15 @@
         <v>2</v>
       </c>
       <c r="H119" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I119" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B120" s="6"/>
       <c r="C120" s="6" t="n">
@@ -2622,15 +2652,15 @@
         <v>6</v>
       </c>
       <c r="H120" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I120" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B121" s="6"/>
       <c r="C121" s="6"/>
@@ -2641,15 +2671,15 @@
         <v>5</v>
       </c>
       <c r="H121" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I121" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B122" s="6"/>
       <c r="C122" s="6"/>
@@ -2660,15 +2690,15 @@
         <v>9</v>
       </c>
       <c r="H122" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I122" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B123" s="6"/>
       <c r="C123" s="6"/>
@@ -2679,15 +2709,15 @@
         <v>1</v>
       </c>
       <c r="H123" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I123" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B124" s="6"/>
       <c r="C124" s="6"/>
@@ -2698,15 +2728,15 @@
         <v>8</v>
       </c>
       <c r="H124" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I124" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B125" s="6"/>
       <c r="C125" s="6"/>
@@ -2719,15 +2749,15 @@
         <v>7</v>
       </c>
       <c r="H125" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I125" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -2738,10 +2768,10 @@
         <v>4</v>
       </c>
       <c r="H126" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I126" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2759,14 +2789,14 @@
       <c r="A128" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B128" s="2" t="n">
-        <v>6</v>
+      <c r="B128" s="2" t="s">
+        <v>104</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E128" s="3" t="n">
         <v>44072</v>
@@ -2789,19 +2819,19 @@
     </row>
     <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B130" s="3" t="n">
         <v>44072</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="4"/>
@@ -2821,7 +2851,7 @@
     </row>
     <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -2832,15 +2862,15 @@
         <v>3</v>
       </c>
       <c r="H132" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -2851,15 +2881,15 @@
         <v>2</v>
       </c>
       <c r="H133" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I133" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B134" s="6"/>
       <c r="C134" s="6"/>
@@ -2872,15 +2902,15 @@
         <v>6</v>
       </c>
       <c r="H134" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I134" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="B135" s="6" t="n">
         <v>4</v>
@@ -2897,15 +2927,15 @@
         <v>1</v>
       </c>
       <c r="H135" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I135" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B136" s="6"/>
       <c r="C136" s="6" t="n">
@@ -2920,15 +2950,15 @@
         <v>4</v>
       </c>
       <c r="H136" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I136" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -2939,10 +2969,10 @@
         <v>5</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
